--- a/gd/excel/ItemType.xlsx
+++ b/gd/excel/ItemType.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +26,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <name val="Aptos"/>
+      <color rgb="00475569"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -47,24 +40,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C9A227"/>
-        <bgColor rgb="00C9A227"/>
+        <fgColor rgb="00FBE6A5"/>
+        <bgColor rgb="00FBE6A5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00DCE3EC"/>
+        <bgColor rgb="00DCE3EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B4332"/>
-        <bgColor rgb="001B4332"/>
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -78,59 +71,78 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00EDF7EE"/>
-          <bgColor rgb="00EDF7EE"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00CCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="00CCCCCC"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00CCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="00CCCCCC"/>
-        </right>
-      </border>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -500,40 +512,40 @@
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类型唯一ID，禁止修改</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>类型名称（多语言）</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>类型代码，程序引用用</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Id
 int32</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Name
-string[i18n]</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+string</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Code
 string</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>类型唯一ID，禁止修改</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>类型名称（多语言）</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>类型代码，程序引用用</t>
         </is>
       </c>
     </row>
@@ -583,14 +595,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:C1000">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A3:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>